--- a/data/random_collections/TabS5_oligos.xlsx
+++ b/data/random_collections/TabS5_oligos.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felix\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\prime-seq_NextGen\data\random_collections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB02A7E3-1247-447E-89B1-3E7B9C82FCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13170"/>
   </bookViews>
   <sheets>
     <sheet name="Oligos" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
   <si>
     <t>Name</t>
   </si>
@@ -161,12 +160,27 @@
   </si>
   <si>
     <t>Biotin-ACACTCTTTCCCTACACGACGCGGG</t>
+  </si>
+  <si>
+    <t>Library ReAmp primer forward</t>
+  </si>
+  <si>
+    <t>AATGATACGGCGACCACCGA</t>
+  </si>
+  <si>
+    <t>CAAGCAGAAGACGGCATACGAG</t>
+  </si>
+  <si>
+    <t>Library ReAmp primer reverse</t>
+  </si>
+  <si>
+    <t>for library re-amplification</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -406,9 +420,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -416,7 +430,7 @@
     <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -444,7 +458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -458,7 +472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -472,7 +486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -486,7 +500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -500,7 +514,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -514,7 +528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
@@ -528,7 +542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -542,7 +556,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -556,7 +570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -570,7 +584,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -584,7 +598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
@@ -598,7 +612,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
@@ -612,7 +626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
@@ -626,7 +640,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
@@ -640,7 +654,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
@@ -652,6 +666,34 @@
       </c>
       <c r="D17" s="2" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
